--- a/data/relacionamento-atualizado-2026-07-23.xlsx
+++ b/data/relacionamento-atualizado-2026-07-23.xlsx
@@ -4071,12 +4071,12 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>043 - CURVA F</t>
+          <t>014 - FERRAMENTAS E CONSTRUCAO</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Isabely</t>
+          <t>Duilio</t>
         </is>
       </c>
       <c r="E152" s="5" t="n"/>
@@ -6477,12 +6477,12 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>043 - CURVA F</t>
+          <t>001 - AUTO PECAS</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Isabely</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="E252" s="5" t="n"/>
@@ -6500,12 +6500,12 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>043 - CURVA F</t>
+          <t>001 - AUTO PECAS</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Isabely</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="E253" s="5" t="n"/>
@@ -15546,12 +15546,12 @@
       </c>
       <c r="C635" s="4" t="inlineStr">
         <is>
-          <t>043 - CURVA F</t>
+          <t>006 - DISTRIBUIDOR DE COSMETICOS</t>
         </is>
       </c>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>Isabely</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="E635" s="5" t="n"/>
